--- a/upload/pagamentorp2026.xlsx
+++ b/upload/pagamentorp2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="dados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1181293.94</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1181293.94</t>
         </is>
       </c>
     </row>

--- a/upload/pagamentorp2026.xlsx
+++ b/upload/pagamentorp2026.xlsx
@@ -3470,7 +3470,7 @@
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23850</t>
         </is>
       </c>
     </row>

--- a/upload/pagamentorp2026.xlsx
+++ b/upload/pagamentorp2026.xlsx
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4000000</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">

--- a/upload/pagamentorp2026.xlsx
+++ b/upload/pagamentorp2026.xlsx
@@ -3378,7 +3378,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42155126.18</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
